--- a/tests/integration_workspace/dashboard_full_pipeline/output/price_match.xlsx
+++ b/tests/integration_workspace/dashboard_full_pipeline/output/price_match.xlsx
@@ -494,7 +494,11 @@
           <t>SKU-APPLE</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SVO shampoo apple 1 l</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>A-100</t>
@@ -524,7 +528,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-08-05T18:55:03.233973+00:00</t>
+          <t>2026-08-06T16:37:00.557317+00:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -544,7 +548,11 @@
           <t>SKU-LIME</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SVO shampoo lime 1 l</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>A-200</t>
@@ -574,7 +582,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-08-05T18:55:03.233973+00:00</t>
+          <t>2026-08-06T16:37:00.557317+00:00</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/tests/integration_workspace/dashboard_full_pipeline/output/price_match.xlsx
+++ b/tests/integration_workspace/dashboard_full_pipeline/output/price_match.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-08-06T16:37:00.557317+00:00</t>
+          <t>2026-09-03T09:07:46.189545+00:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-08-06T16:37:00.557317+00:00</t>
+          <t>2026-09-03T09:07:46.189545+00:00</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
